--- a/utils/monday_sprint_sprint_2025-17.xlsx
+++ b/utils/monday_sprint_sprint_2025-17.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="279">
   <si>
     <t>Ticket</t>
   </si>
@@ -165,7 +165,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -495,6 +495,9 @@
     <t>10/02/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Fevereiro</t>
   </si>
   <si>
@@ -747,31 +750,25 @@
     <t>Editar posição dos pontos</t>
   </si>
   <si>
-    <t>33591</t>
-  </si>
-  <si>
-    <t>Irog ajustagem</t>
+    <t>33489</t>
+  </si>
+  <si>
+    <t>Implementação sistema retrabalho Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Boa tarde! Conforme tratativas já feitas anteriores @Edson João Hammermeister, oficializo a abertura do chamado para criação da aplicação no SENSE com foco no retrabalho do Tratamento Térmico. Conforme já conversamos, o Lucas, antes de seu desligamento da Altona, já havia deixado esta aplicação prat</t>
+  </si>
+  <si>
+    <t>Fernanda da Costa Rodrigues</t>
+  </si>
+  <si>
+    <t>13/08/2025</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
   </si>
   <si>
     <t>Fila</t>
-  </si>
-  <si>
-    <t>33489</t>
-  </si>
-  <si>
-    <t>Implementação sistema retrabalho Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Boa tarde! Conforme tratativas já feitas anteriores @Edson João Hammermeister, oficializo a abertura do chamado para criação da aplicação no SENSE com foco no retrabalho do Tratamento Térmico. Conforme já conversamos, o Lucas, antes de seu desligamento da Altona, já havia deixado esta aplicação prat</t>
-  </si>
-  <si>
-    <t>Fernanda da Costa Rodrigues</t>
-  </si>
-  <si>
-    <t>13/08/2025</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
   </si>
   <si>
     <t>Agosto</t>
@@ -1269,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3869,7 +3866,7 @@
         <v>159</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>20</v>
@@ -3878,7 +3875,7 @@
         <v>31</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -3895,7 +3892,7 @@
         <v>36</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>17</v>
@@ -3927,7 +3924,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3939,10 +3936,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
@@ -3971,7 +3968,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3983,10 +3980,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -4015,7 +4012,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4027,10 +4024,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -4071,7 +4068,7 @@
         <v>36</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>17</v>
@@ -4103,7 +4100,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4115,10 +4112,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -4147,7 +4144,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4159,10 +4156,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4191,7 +4188,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4203,10 +4200,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4235,7 +4232,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4247,10 +4244,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4268,7 +4265,7 @@
         <v>17</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>31</v>
@@ -4279,7 +4276,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4291,10 +4288,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4323,7 +4320,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4335,22 +4332,22 @@
         <v>36</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>17</v>
@@ -4362,12 +4359,12 @@
         <v>28</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4379,10 +4376,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4411,7 +4408,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4423,10 +4420,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4455,7 +4452,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4467,10 +4464,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4499,7 +4496,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4511,10 +4508,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>38</v>
@@ -4543,7 +4540,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4555,10 +4552,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4587,7 +4584,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4599,10 +4596,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4631,7 +4628,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4643,39 +4640,39 @@
         <v>36</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>44</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4687,10 +4684,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4719,7 +4716,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4731,10 +4728,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4763,7 +4760,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4775,10 +4772,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4807,7 +4804,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4819,10 +4816,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4851,7 +4848,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4863,10 +4860,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>19</v>
@@ -4895,7 +4892,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4907,10 +4904,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4939,7 +4936,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -4951,10 +4948,10 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
@@ -4983,7 +4980,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -4995,10 +4992,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -5027,7 +5024,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5039,10 +5036,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -5071,7 +5068,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5083,10 +5080,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -5115,7 +5112,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5127,10 +5124,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -5159,7 +5156,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5171,10 +5168,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5203,7 +5200,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5215,10 +5212,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
@@ -5247,7 +5244,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5259,10 +5256,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>19</v>
@@ -5291,7 +5288,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5303,10 +5300,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>19</v>
@@ -5335,7 +5332,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5347,10 +5344,10 @@
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>19</v>
@@ -5379,7 +5376,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5391,10 +5388,10 @@
         <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>19</v>
@@ -5423,7 +5420,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5435,10 +5432,10 @@
         <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
@@ -5467,7 +5464,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5479,10 +5476,10 @@
         <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>19</v>
@@ -5511,7 +5508,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5523,10 +5520,10 @@
         <v>17</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>19</v>
@@ -5555,7 +5552,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -5567,10 +5564,10 @@
         <v>17</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>19</v>
@@ -5599,7 +5596,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -5608,81 +5605,37 @@
         <v>16</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>17</v>
+        <v>248</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>17</v>
+        <v>249</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>17</v>
+        <v>250</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="K100" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="L100" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N100" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -5698,23 +5651,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" t="s">
         <v>255</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>256</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>257</v>
-      </c>
-      <c r="E2" t="s">
-        <v>258</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5722,21 +5675,21 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -5750,7 +5703,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5763,7 +5716,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -5771,7 +5724,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5802,15 +5755,15 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5831,25 +5784,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="P9" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="Q9" s="6" t="s">
         <v>270</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5857,22 +5810,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5904,10 +5857,10 @@
         <v>16</v>
       </c>
       <c r="J11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K11">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s">
         <v>24</v>
@@ -5919,7 +5872,7 @@
         <v>31</v>
       </c>
       <c r="Q11">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -5933,7 +5886,7 @@
         <v>19</v>
       </c>
       <c r="H12">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M12" t="s">
         <v>92</v>
@@ -5945,7 +5898,7 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -5956,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5976,13 +5929,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -5998,15 +5951,15 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6014,7 +5967,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6025,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6039,7 +5992,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>46</v>
@@ -6047,16 +6000,16 @@
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6067,7 +6020,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>156</v>
@@ -6075,16 +6028,16 @@
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6095,7 +6048,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>94</v>
@@ -6109,7 +6062,7 @@
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>151</v>
@@ -6123,7 +6076,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>37</v>
@@ -6137,7 +6090,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>43</v>
@@ -6151,7 +6104,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>62</v>
@@ -6165,7 +6118,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>76</v>

--- a/utils/monday_sprint_sprint_2025-17.xlsx
+++ b/utils/monday_sprint_sprint_2025-17.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="293">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>29123</t>
+    <t>8092916186</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,90 +87,99 @@
     <t>20/12/2024</t>
   </si>
   <si>
+    <t>12/08/2025</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>9279941653</t>
+  </si>
+  <si>
+    <t>SISTEMA DE ENSAIOS MECÂNICOS DE PEÇA - Analise</t>
+  </si>
+  <si>
+    <t>02/06/2025</t>
+  </si>
+  <si>
+    <t>10/08/2025</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>9471887715</t>
+  </si>
+  <si>
+    <t>Criação de dashboard</t>
+  </si>
+  <si>
+    <t>27/06/2025</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>9778909961</t>
+  </si>
+  <si>
+    <t>Sistema de Certificado (qualidade)</t>
+  </si>
+  <si>
+    <t>08/08/2025</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>9778921468</t>
+  </si>
+  <si>
+    <t>APONTAMENTOS ELTRONICOS LINHAS ACABAMAENTO</t>
+  </si>
+  <si>
+    <t>24/08/2025</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Integração CRM - Setor consumo</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>31347</t>
-  </si>
-  <si>
-    <t>SISTEMA DE ENSAIOS MECÂNICOS DE PEÇA - Analise</t>
-  </si>
-  <si>
-    <t>02/06/2025</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>32407</t>
-  </si>
-  <si>
-    <t>Criação de dashboard</t>
-  </si>
-  <si>
-    <t>27/06/2025</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>33076</t>
-  </si>
-  <si>
-    <t>Sistema de Certificado (qualidade)</t>
-  </si>
-  <si>
-    <t>08/08/2025</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>33064</t>
-  </si>
-  <si>
-    <t>APONTAMENTOS ELTRONICOS LINHAS ACABAMAENTO</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Integração CRM - Setor consumo</t>
-  </si>
-  <si>
     <t>Alta</t>
   </si>
   <si>
@@ -183,13 +192,16 @@
     <t>11/08/2025</t>
   </si>
   <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
     <t>Integração CRM - Tarefa para disparar integrações</t>
   </si>
   <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>9572712934</t>
   </si>
   <si>
     <t>Consulta de divergências - Registro Pintura</t>
@@ -201,25 +213,28 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>33116</t>
+    <t>9778615669</t>
   </si>
   <si>
     <t>Adicionar coluna no sistema de moldagem USE-ULE para tradução das perguntas</t>
   </si>
   <si>
-    <t>32998</t>
+    <t>9778935539</t>
   </si>
   <si>
     <t>Inclusão valor do aço e peso do aço na invoice</t>
   </si>
   <si>
-    <t>31701</t>
+    <t>9787746498</t>
   </si>
   <si>
     <t>IA para a predição e dimensionamento de estoque</t>
   </si>
   <si>
-    <t>32677</t>
+    <t>23/08/2025</t>
+  </si>
+  <si>
+    <t>9584224135</t>
   </si>
   <si>
     <t>PDI - Inspeção - Cotas informadas.</t>
@@ -228,7 +243,7 @@
     <t>14/07/2025</t>
   </si>
   <si>
-    <t>32863</t>
+    <t>9787355407</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DE TELAS DO PCP PARA SEQUÊNCIAS DE PRÉ-PRODUTIVO</t>
@@ -237,7 +252,7 @@
     <t>Integração CRM - Representantes</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>9581460605</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -246,31 +261,34 @@
     <t>Controle do status por declaração</t>
   </si>
   <si>
-    <t>32314</t>
+    <t>9787337507</t>
   </si>
   <si>
     <t>Peso p/ Usinagem</t>
   </si>
   <si>
-    <t>33361</t>
+    <t>17/08/2025</t>
+  </si>
+  <si>
+    <t>9777686045</t>
   </si>
   <si>
     <t>Alteração da Tela de Visualização - Registros de Moldagem</t>
   </si>
   <si>
-    <t>33383</t>
+    <t>9777637658</t>
   </si>
   <si>
     <t>Gestão de orçamento por gerência</t>
   </si>
   <si>
-    <t>32933</t>
+    <t>9787650401</t>
   </si>
   <si>
     <t>CRIAÇÃO DE DASHBOARDS - INDICADORES INSTALAÇÃO INDUSTRIAL</t>
   </si>
   <si>
-    <t>33258</t>
+    <t>9778251079</t>
   </si>
   <si>
     <t>Dados na impressão de pré-lista EPI</t>
@@ -279,19 +297,22 @@
     <t>Integração CRM - Tipo de pagamento</t>
   </si>
   <si>
-    <t>33380</t>
+    <t>9777653897</t>
   </si>
   <si>
     <t>Roteiro - Atividade Complementar (Usinagem)</t>
   </si>
   <si>
-    <t>32665</t>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>9787650483</t>
   </si>
   <si>
     <t>Computador ajustagem - Desenvolvimento</t>
   </si>
   <si>
-    <t>32092</t>
+    <t>9374693703</t>
   </si>
   <si>
     <t>criar campo quantitativo no itens verificados em preventiva</t>
@@ -300,19 +321,19 @@
     <t>13/06/2025</t>
   </si>
   <si>
-    <t>33248</t>
+    <t>9778270346</t>
   </si>
   <si>
     <t>Mudanças no sistema de EPI</t>
   </si>
   <si>
-    <t>33230</t>
+    <t>9778291467</t>
   </si>
   <si>
     <t>Cadastro de Instruções de Soldagem no CPP</t>
   </si>
   <si>
-    <t>32584</t>
+    <t>9572556420</t>
   </si>
   <si>
     <t>Sistema para monitoramento de ruído</t>
@@ -321,7 +342,7 @@
     <t>Homologação</t>
   </si>
   <si>
-    <t>32310</t>
+    <t>9787650606</t>
   </si>
   <si>
     <t>Retrabalho da moldagem - Classificação</t>
@@ -330,76 +351,76 @@
     <t>Impedimento</t>
   </si>
   <si>
-    <t>32079</t>
-  </si>
-  <si>
-    <t>TI</t>
+    <t>9787342695</t>
   </si>
   <si>
     <t>Directa MES - Especificação Transferência NC</t>
   </si>
   <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
     <t>Integração CRM - Estados</t>
   </si>
   <si>
-    <t>33360</t>
+    <t>9777701219</t>
   </si>
   <si>
     <t>Auditoria MPO, PID e Checklist</t>
   </si>
   <si>
-    <t>32771</t>
+    <t>9787460192</t>
   </si>
   <si>
     <t>Ajustar a baixa de oferta quando foi perdida/cancelada e Alterar os relatórios de Orçamentos Cancelados e Pe</t>
   </si>
   <si>
+    <t>9584226870</t>
+  </si>
+  <si>
     <t>PDI - Alterar/Excluir Sequência inserida</t>
   </si>
   <si>
-    <t>33044</t>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>9787650549</t>
   </si>
   <si>
     <t>Correção dos motivos de paradas</t>
   </si>
   <si>
-    <t>33249</t>
+    <t>9778262081</t>
   </si>
   <si>
     <t>Melhoria no sistema pré-lista EPI</t>
   </si>
   <si>
-    <t>32793</t>
+    <t>9787511341</t>
   </si>
   <si>
     <t>Ensaios FTFs Liebherr</t>
   </si>
   <si>
-    <t>31818</t>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>9787495627</t>
   </si>
   <si>
     <t>Atualização Status Romaneio</t>
   </si>
   <si>
-    <t>33374</t>
+    <t>9777665299</t>
   </si>
   <si>
     <t>Melhoria relatório 2ª corda</t>
   </si>
   <si>
-    <t>33343</t>
+    <t>9777873333</t>
   </si>
   <si>
     <t>Adição de campo dimensão Inventário de caixas</t>
   </si>
   <si>
-    <t>32963</t>
+    <t>9674243165</t>
   </si>
   <si>
     <t>Sistema WMS ajuste na baixa de pré-lista</t>
@@ -408,79 +429,88 @@
     <t>25/07/2025</t>
   </si>
   <si>
-    <t>33352</t>
+    <t>9777863224</t>
   </si>
   <si>
     <t>CONSULTA DE NORMAS - MASTERLIST</t>
   </si>
   <si>
-    <t>33332</t>
+    <t>13/08/2025</t>
+  </si>
+  <si>
+    <t>9778003223</t>
   </si>
   <si>
     <t>DADOS ADICIONAIS CONSIGNADO</t>
   </si>
   <si>
-    <t>33023</t>
+    <t>9674141551</t>
   </si>
   <si>
     <t>Desenvolvimento de aplicação de custos por refugo</t>
   </si>
   <si>
-    <t>32853</t>
+    <t>9787501866</t>
   </si>
   <si>
     <t>Ajuste Polaris - Item Cadastros</t>
   </si>
   <si>
-    <t>33353</t>
+    <t>9777717750</t>
   </si>
   <si>
     <t>Controle de Operador x Setor habilitado para movimentar (usinagem)</t>
   </si>
   <si>
-    <t>31609</t>
+    <t>9787736528</t>
   </si>
   <si>
     <t>ALERTA DE REVISÃO X BLOQUEIO DE MODELO</t>
   </si>
   <si>
-    <t>32723</t>
+    <t>9787753214</t>
   </si>
   <si>
     <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
   </si>
   <si>
-    <t>32025</t>
+    <t>9787486000</t>
   </si>
   <si>
     <t>Verificação do sistema WMS – Servidores VMSRV_RDS_02 e VMSRV_RDS_03</t>
   </si>
   <si>
-    <t>32643</t>
+    <t>16/08/2025</t>
+  </si>
+  <si>
+    <t>9787531731</t>
   </si>
   <si>
     <t>Altona || Alteração de notas X Alteração de Estoque</t>
   </si>
   <si>
-    <t>32082</t>
+    <t>9787711340</t>
   </si>
   <si>
     <t>PROCEDIMENTO PRÉ-PRODUTIVO SETOR 540</t>
   </si>
   <si>
-    <t>31699</t>
+    <t>9787770597</t>
   </si>
   <si>
     <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
   </si>
   <si>
+    <t>9584229817</t>
+  </si>
+  <si>
     <t>PDI - Fixar colunas de identificação das cotas</t>
   </si>
   <si>
     <t>Integração CRM - Carga Unidade Federação</t>
   </si>
   <si>
-    <t>33334</t>
+    <t>9777981269</t>
   </si>
   <si>
     <t>Correção</t>
@@ -489,13 +519,13 @@
     <t>Erro: Aplicação QlikSense Produção das Linhas</t>
   </si>
   <si>
-    <t>31794</t>
+    <t>9787770804</t>
   </si>
   <si>
     <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>9684140290</t>
   </si>
   <si>
     <t>Conversão KB TOTO</t>
@@ -504,21 +534,18 @@
     <t>28/07/2025</t>
   </si>
   <si>
-    <t>32353</t>
+    <t>9787637136</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo (copy)</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexandre, bom dia! Para Custeio Usinagem Pintura, ao invés de utilizar apontamentos de horas, valores do setor PINTURA (centro custo 8010) devem ser rateados somente para as sequências movimentadas no setor 3081. Critério de rateio deve ser proporcional de custo FTF dos setores 3081 + 3082 + 8010. </t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Saneamento de dados para APS</t>
   </si>
   <si>
@@ -534,19 +561,19 @@
     <t>Integração CRM - Carga Ofertas</t>
   </si>
   <si>
-    <t>33229</t>
+    <t>9778314528</t>
   </si>
   <si>
     <t>Link Parâmetros de IS com Apontamento de Solda Digital</t>
   </si>
   <si>
-    <t>33222</t>
+    <t>9778329567</t>
   </si>
   <si>
     <t>Atualizar planilha com novo campo</t>
   </si>
   <si>
-    <t>33314</t>
+    <t>9778045514</t>
   </si>
   <si>
     <t>Apoio/Cálculo custo - Inspeção - ajuste no filtro dos apontamento.</t>
@@ -555,25 +582,25 @@
     <t>Integração CRM - Transportadora</t>
   </si>
   <si>
-    <t>33308</t>
+    <t>9778052591</t>
   </si>
   <si>
     <t>Criar parada - apontamento eletrônico</t>
   </si>
   <si>
-    <t>33209</t>
+    <t>9778423696</t>
   </si>
   <si>
     <t>Analise de tempo de manutenção</t>
   </si>
   <si>
-    <t>33300</t>
+    <t>9778073283</t>
   </si>
   <si>
     <t>Alteração tela consulta de etiquetas</t>
   </si>
   <si>
-    <t>31700</t>
+    <t>9787746091</t>
   </si>
   <si>
     <t>IA para programação automática de máquinas de usinagem</t>
@@ -582,49 +609,49 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>33210</t>
+    <t>9778406762</t>
   </si>
   <si>
     <t>Setor 7299 Amostra</t>
   </si>
   <si>
-    <t>31836</t>
+    <t>9787771225</t>
   </si>
   <si>
     <t>Melhoria WMS - Conferencia e Carregamento</t>
   </si>
   <si>
-    <t>33217</t>
+    <t>9778365302</t>
   </si>
   <si>
     <t>Altona || Relatório para controle das compras de consignados</t>
   </si>
   <si>
-    <t>31314</t>
+    <t>9683896045</t>
   </si>
   <si>
     <t>Solicitação de Exportação de Planilha – Modelos e Centros de Usinagem</t>
   </si>
   <si>
-    <t>33402</t>
+    <t>9777618163</t>
   </si>
   <si>
     <t>CÓPIA DE CHECKLIST DE PRÉ-PRODUTIVO - PERGUNTA ALERTA DE REVISÃO</t>
   </si>
   <si>
-    <t>32041</t>
+    <t>9787888811</t>
   </si>
   <si>
     <t>Custos de Armazenagem/MP</t>
   </si>
   <si>
-    <t>33095</t>
+    <t>9787746330</t>
   </si>
   <si>
     <t>Bloqueio Número Modelo CPP e Cliente - FTF, OTF e CPP</t>
   </si>
   <si>
-    <t>32088</t>
+    <t>9787889036</t>
   </si>
   <si>
     <t>criar arvore de componentes</t>
@@ -633,6 +660,9 @@
     <t>29853</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
   </si>
   <si>
@@ -645,144 +675,144 @@
     <t>ADH</t>
   </si>
   <si>
-    <t>33202</t>
+    <t>9778456951</t>
   </si>
   <si>
     <t>Ajuste em requisições de materiais de estoque</t>
   </si>
   <si>
-    <t>33162</t>
+    <t>9778512104</t>
   </si>
   <si>
     <t>Melhoria no sistema endereçamento WMS</t>
   </si>
   <si>
-    <t>33286</t>
+    <t>9778094486</t>
   </si>
   <si>
     <t>Checklist Máquina -&gt; Componente -&gt; Status (Sistema Manutenção)</t>
   </si>
   <si>
-    <t>33190</t>
+    <t>9778486265</t>
   </si>
   <si>
     <t>Tela de Lançamento – Contas Contábeis Não Editáveis</t>
   </si>
   <si>
-    <t>33163</t>
+    <t>9778501175</t>
   </si>
   <si>
     <t>Prioridade de endereço mais antigo com saldo</t>
   </si>
   <si>
-    <t>32857</t>
+    <t>9787889153</t>
   </si>
   <si>
     <t>Melhorias dentro do sistema wms pré-lista</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>9787889462</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>32849</t>
+    <t>9787889572</t>
   </si>
   <si>
     <t>ALTERAÇÃO VENCIMENTO VOLVO DO BRASIL</t>
   </si>
   <si>
-    <t>33153</t>
+    <t>9778578907</t>
   </si>
   <si>
     <t>Melhoria Sistema de SS/OS - Manutenção</t>
   </si>
   <si>
-    <t>33158</t>
+    <t>9778551083</t>
   </si>
   <si>
     <t>layout WMS sistema pré-lista cascata</t>
   </si>
   <si>
-    <t>33161</t>
+    <t>9778522746</t>
   </si>
   <si>
     <t>Prioridade no sistema pré-lista por rua-prédio-nível</t>
   </si>
   <si>
-    <t>32858</t>
+    <t>9787889325</t>
   </si>
   <si>
     <t>[NIMBI] API's para a integração de requisição gerado no ERP &gt; Nimbi</t>
   </si>
   <si>
-    <t>33079</t>
+    <t>9673881130</t>
   </si>
   <si>
     <t>Controle de indicadores ao vivo (Parte Fabril).</t>
   </si>
   <si>
-    <t>32926</t>
+    <t>27/07/2025</t>
+  </si>
+  <si>
+    <t>9674669283</t>
   </si>
   <si>
     <t>Programa 5S - Criação de novo setor dentro do sistema</t>
   </si>
   <si>
-    <t>33027</t>
+    <t>9674112450</t>
   </si>
   <si>
     <t>Extração de dados usinagem - IA máquinas de usinagem</t>
   </si>
   <si>
-    <t>33424</t>
+    <t>9793425479</t>
   </si>
   <si>
     <t>Adição de Coluna no gráfico do refugo</t>
   </si>
   <si>
-    <t>32945</t>
+    <t>9793641035</t>
   </si>
   <si>
     <t>Aplicativo Corte de canais Pó de ferro - Instrução de Paradas</t>
   </si>
   <si>
-    <t>32298</t>
+    <t>9803424920</t>
   </si>
   <si>
     <t>Mais de um mapeamento por sequência</t>
   </si>
   <si>
-    <t>12/08/2025</t>
+    <t>9803432886</t>
   </si>
   <si>
     <t>Inclusão de opções de estágio de fabricação</t>
   </si>
   <si>
+    <t>9803439954</t>
+  </si>
+  <si>
     <t>Sistema avisar quando coloca uma largura maior que o comprimento</t>
   </si>
   <si>
+    <t>9803444802</t>
+  </si>
+  <si>
     <t>Editar posição dos pontos</t>
   </si>
   <si>
-    <t>33489</t>
+    <t>9880064041</t>
   </si>
   <si>
     <t>Implementação sistema retrabalho Tratamento Térmico</t>
   </si>
   <si>
-    <t>Boa tarde! Conforme tratativas já feitas anteriores @Edson João Hammermeister, oficializo a abertura do chamado para criação da aplicação no SENSE com foco no retrabalho do Tratamento Térmico. Conforme já conversamos, o Lucas, antes de seu desligamento da Altona, já havia deixado esta aplicação prat</t>
-  </si>
-  <si>
-    <t>Fernanda da Costa Rodrigues</t>
-  </si>
-  <si>
     <t>22/08/2025</t>
   </si>
   <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
     <t>Fila</t>
   </si>
   <si>
@@ -792,7 +822,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-17</t>
+    <t>Dez/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1422,13 +1452,13 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -1469,13 +1499,13 @@
         <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>39</v>
@@ -1516,7 +1546,7 @@
         <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1525,15 +1555,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1545,10 +1575,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1563,7 +1593,7 @@
         <v>42</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1572,45 +1602,45 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1619,62 +1649,62 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1686,10 +1716,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1701,27 +1731,27 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1733,10 +1763,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1751,7 +1781,7 @@
         <v>42</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1760,15 +1790,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1780,10 +1810,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1798,7 +1828,7 @@
         <v>42</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1807,30 +1837,30 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1842,10 +1872,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1854,15 +1884,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1874,10 +1904,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1889,27 +1919,27 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1921,10 +1951,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1936,10 +1966,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1948,45 +1978,45 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1995,62 +2025,62 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -2062,10 +2092,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -2077,10 +2107,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -2089,15 +2119,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2109,10 +2139,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2127,7 +2157,7 @@
         <v>42</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -2136,15 +2166,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -2156,13 +2186,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -2174,7 +2204,7 @@
         <v>42</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -2183,15 +2213,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2203,10 +2233,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2218,10 +2248,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2230,15 +2260,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2250,10 +2280,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2268,7 +2298,7 @@
         <v>42</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2277,45 +2307,45 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2324,15 +2354,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2344,10 +2374,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2362,7 +2392,7 @@
         <v>42</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2371,15 +2401,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2391,10 +2421,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2406,10 +2436,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2418,15 +2448,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2438,10 +2468,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2453,10 +2483,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2465,7 +2495,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>35</v>
@@ -2473,7 +2503,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2485,10 +2515,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2512,15 +2542,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2532,10 +2562,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2550,7 +2580,7 @@
         <v>42</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2559,15 +2589,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2579,10 +2609,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2594,27 +2624,27 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2626,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2641,57 +2671,57 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2700,45 +2730,45 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2747,15 +2777,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2767,10 +2797,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2785,7 +2815,7 @@
         <v>42</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2794,15 +2824,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2814,10 +2844,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2829,10 +2859,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2841,15 +2871,15 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2861,10 +2891,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2876,10 +2906,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2888,15 +2918,15 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2908,10 +2938,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2923,27 +2953,27 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2955,10 +2985,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2973,7 +3003,7 @@
         <v>42</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2982,15 +3012,15 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -3002,10 +3032,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -3017,10 +3047,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -3029,15 +3059,15 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -3049,10 +3079,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -3064,10 +3094,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -3076,15 +3106,15 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -3096,10 +3126,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -3114,7 +3144,7 @@
         <v>42</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3123,15 +3153,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3143,10 +3173,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3170,15 +3200,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3190,10 +3220,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3205,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>24</v>
@@ -3220,12 +3250,12 @@
         <v>39</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3237,10 +3267,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3255,7 +3285,7 @@
         <v>42</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3264,15 +3294,15 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3284,10 +3314,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3302,7 +3332,7 @@
         <v>42</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3311,15 +3341,15 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3331,13 +3361,13 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -3346,27 +3376,27 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>39</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3378,10 +3408,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3393,27 +3423,27 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3425,10 +3455,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3443,7 +3473,7 @@
         <v>42</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3452,15 +3482,15 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3472,10 +3502,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3487,27 +3517,27 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3519,13 +3549,13 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>21</v>
@@ -3534,27 +3564,27 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3566,10 +3596,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3581,10 +3611,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3593,15 +3623,15 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3613,10 +3643,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3628,10 +3658,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3640,15 +3670,15 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3660,10 +3690,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3675,10 +3705,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3687,33 +3717,33 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>21</v>
@@ -3722,10 +3752,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3734,15 +3764,15 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3754,10 +3784,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3769,57 +3799,57 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3828,30 +3858,30 @@
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3866,7 +3896,7 @@
         <v>42</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3875,15 +3905,15 @@
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3895,10 +3925,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3910,42 +3940,42 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3957,27 +3987,27 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>39</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3986,75 +4016,75 @@
         <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -4063,62 +4093,62 @@
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -4130,10 +4160,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4148,7 +4178,7 @@
         <v>42</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -4157,15 +4187,15 @@
         <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4177,10 +4207,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4195,7 +4225,7 @@
         <v>42</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -4204,15 +4234,15 @@
         <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4224,10 +4254,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4251,45 +4281,45 @@
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4298,15 +4328,15 @@
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4318,10 +4348,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4336,7 +4366,7 @@
         <v>42</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4345,15 +4375,15 @@
         <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4365,10 +4395,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4383,7 +4413,7 @@
         <v>42</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4392,15 +4422,15 @@
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4412,10 +4442,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4430,7 +4460,7 @@
         <v>42</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4439,30 +4469,30 @@
         <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4474,27 +4504,27 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4506,10 +4536,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4524,7 +4554,7 @@
         <v>42</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -4533,15 +4563,15 @@
         <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4553,10 +4583,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4568,27 +4598,27 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4600,10 +4630,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -4618,7 +4648,7 @@
         <v>42</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -4627,15 +4657,15 @@
         <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4647,10 +4677,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4662,10 +4692,10 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>25</v>
@@ -4677,12 +4707,12 @@
         <v>39</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4694,10 +4724,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4712,7 +4742,7 @@
         <v>42</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
@@ -4721,15 +4751,15 @@
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4741,13 +4771,13 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>21</v>
@@ -4756,10 +4786,10 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>25</v>
@@ -4768,15 +4798,15 @@
         <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4788,10 +4818,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4803,10 +4833,10 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>25</v>
@@ -4815,15 +4845,15 @@
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4835,10 +4865,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4850,10 +4880,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>25</v>
@@ -4862,62 +4892,62 @@
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -4929,10 +4959,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4947,7 +4977,7 @@
         <v>42</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -4956,15 +4986,15 @@
         <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -4976,10 +5006,10 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -5003,15 +5033,15 @@
         <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -5023,10 +5053,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -5041,7 +5071,7 @@
         <v>42</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
@@ -5050,15 +5080,15 @@
         <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -5070,10 +5100,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5088,7 +5118,7 @@
         <v>42</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
@@ -5097,15 +5127,15 @@
         <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5117,10 +5147,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
@@ -5135,7 +5165,7 @@
         <v>42</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>25</v>
@@ -5144,15 +5174,15 @@
         <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5164,10 +5194,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5179,10 +5209,10 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5191,30 +5221,30 @@
         <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5226,27 +5256,27 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
@@ -5258,10 +5288,10 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5273,10 +5303,10 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>25</v>
@@ -5285,15 +5315,15 @@
         <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
@@ -5305,10 +5335,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5323,7 +5353,7 @@
         <v>42</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>25</v>
@@ -5332,15 +5362,15 @@
         <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
@@ -5352,10 +5382,10 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5379,15 +5409,15 @@
         <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5399,10 +5429,10 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>20</v>
@@ -5420,21 +5450,21 @@
         <v>24</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
@@ -5446,10 +5476,10 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5461,10 +5491,10 @@
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>25</v>
@@ -5473,15 +5503,15 @@
         <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5493,10 +5523,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5508,27 +5538,27 @@
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>246</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>39</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>16</v>
@@ -5540,10 +5570,10 @@
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
@@ -5555,27 +5585,27 @@
         <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>246</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>39</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
@@ -5587,10 +5617,10 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -5602,27 +5632,27 @@
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>246</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>39</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>16</v>
@@ -5634,10 +5664,10 @@
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
@@ -5649,10 +5679,10 @@
         <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>25</v>
@@ -5661,15 +5691,15 @@
         <v>26</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>16</v>
@@ -5681,10 +5711,10 @@
         <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
@@ -5696,10 +5726,10 @@
         <v>22</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>25</v>
@@ -5708,15 +5738,15 @@
         <v>26</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
@@ -5728,10 +5758,10 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -5743,10 +5773,10 @@
         <v>22</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>25</v>
@@ -5755,15 +5785,15 @@
         <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>16</v>
@@ -5775,10 +5805,10 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -5790,7 +5820,7 @@
         <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>24</v>
@@ -5802,15 +5832,15 @@
         <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>16</v>
@@ -5822,10 +5852,10 @@
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -5837,7 +5867,7 @@
         <v>22</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>24</v>
@@ -5849,15 +5879,15 @@
         <v>26</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>16</v>
@@ -5869,10 +5899,10 @@
         <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
@@ -5884,7 +5914,7 @@
         <v>22</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>24</v>
@@ -5896,15 +5926,15 @@
         <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>16</v>
@@ -5913,40 +5943,40 @@
         <v>17</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>255</v>
+        <v>26</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>39</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -5962,23 +5992,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5986,16 +6016,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6006,15 +6036,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>282</v>
+        <v>17.94</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6027,7 +6057,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -6035,7 +6065,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6066,12 +6096,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -6085,35 +6115,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>282</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6121,7 +6151,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6130,13 +6160,13 @@
         <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6148,27 +6178,27 @@
         <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q10">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11">
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H11">
         <v>16</v>
@@ -6177,10 +6207,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N11">
         <v>15</v>
@@ -6189,18 +6219,18 @@
         <v>27</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -6212,13 +6242,13 @@
         <v>82</v>
       </c>
       <c r="J12" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="K12">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -6227,24 +6257,30 @@
         <v>39</v>
       </c>
       <c r="Q12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N13">
         <v>4</v>
@@ -6252,13 +6288,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -6266,7 +6302,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -6274,7 +6310,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -6282,7 +6318,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6290,10 +6326,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -6301,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6309,142 +6345,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>267</v>
+        <v>530</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>168</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
